--- a/data.mn/public/datasets/hospital-beds-national-en.xlsx
+++ b/data.mn/public/datasets/hospital-beds-national-en.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -720,6 +720,14 @@
         <v>30117</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B38" t="n">
+        <v>29465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
